--- a/output/проверьте_названия_Word_и_Excel.xlsx
+++ b/output/проверьте_названия_Word_и_Excel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,40 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Строка в Word</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Колонка в Word</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Excel-источник</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Показатель в Excel</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Колонка Excel</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Строка в column_mapping_v2.csv</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Сколько страниц</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Что сделала программа</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Что сделать</t>
         </is>
@@ -476,969 +481,1067 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+          <t>Строка не узнана</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Таблицы 4, 6, 7, 8, 9, 10, 11, 12, 14, 15, 20, 21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>S25_000000_t01Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Название строки «деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей» не найдено в справочнике ОКВЭД (input/mappings/okved_mapping.csv). Строка не заполнена — в ней прочерки.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Похожей строки в справочнике нет. Если эта строка есть в Excel-источнике (S25_000000_t01Ved14.xlsx) — добавьте её в справочник: строка «код;название», код как в первой колонке Excel, название как в Word. Если в Excel её нет — прочерк правильный, ничего делать не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Таблица «15. группировка организаций, получивших прибыль или убыток, по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I3" t="n">
         <v>72</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Таблица 15 «Группировка организаций, получивших прибыль или убыток, по видам экономической деятельности», страница «Продолжение таблицы 15»</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>производство текстильных изделий</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I4" t="n">
         <v>72</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Таблица «16. группировка организаций, получивших прибыль или убыток, по муниципальным образованиям камчатского края»</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Камчатский край</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I5" t="n">
         <v>87</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14mo8.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14mo8.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Таблица «17. группировка организаций, получивших прибыль или убыток, по организационно-правовым формам»</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Организационно-правовые формы юридических лиц, являющихся коммерческими корпоративными организациями</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I6" t="n">
         <v>102</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25OpfVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25OpfVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Таблица 17 «Группировка организаций, получивших прибыль или убыток, по организационно-правовым формам», страница «Продолжение таблицы 17»</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>потребительские кооперативы</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I7" t="n">
         <v>102</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25OpfVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25OpfVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Таблица «18. группировка организаций, получивших прибыль или убыток, по формам собственности»</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I8" t="n">
         <v>117</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25FsVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25FsVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Строка не узнана</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Таблица 18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Название строки «Всего» не найдено в справочнике категорий (из самого Excel-файла). Строка не заполнена — в ней прочерки.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Похожей строки в справочнике нет. Если эта строка есть в Excel-источнике (S25_000000_t25FsVed14.xlsx) — добавьте её в справочник: строка «код;название», код как в первой колонке Excel, название как в Word. Если в Excel её нет — прочерк правильный, ничего делать не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / всем активам</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>3 (столбец C)</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I10" t="n">
         <v>142</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / всем активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 3 (столбец C).</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам» на «Прибыль, убыток (-) до налогообложения в % к / всем активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / всем активам».</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I11" t="n">
         <v>143</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>5 (столбец E)</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I12" t="n">
         <v>144</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 5 (столбец E).</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>6 (столбец F)</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I13" t="n">
         <v>145</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 6 (столбец F).</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам» на «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>7 (столбец G)</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I14" t="n">
         <v>146</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 7 (столбец G).</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>8 (столбец H)</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I15" t="n">
         <v>147</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 8 (столбец H).</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / всем активам</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>3 (столбец C)</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I16" t="n">
         <v>142</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J16" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / всем активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 3 (столбец C).</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам» на «Прибыль, убыток (-) до налогообложения в % к / всем активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / всем активам».</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I17" t="n">
         <v>143</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J17" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>5 (столбец E)</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I18" t="n">
         <v>144</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J18" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 5 (столбец E).</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>6 (столбец F)</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I19" t="n">
         <v>145</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J19" t="n">
         <v>10</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 6 (столбец F).</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам» на «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>7 (столбец G)</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="I20" t="n">
         <v>146</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 7 (столбец G).</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>8 (столбец H)</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I21" t="n">
         <v>147</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J21" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 8 (столбец H).</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».</t>

--- a/output/проверьте_названия_Word_и_Excel.xlsx
+++ b/output/проверьте_названия_Word_и_Excel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,7 +526,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Таблица «15. группировка организаций, получивших прибыль или убыток, по видам экономической деятельности»</t>
+          <t>Таблица «14. формирование финансовых результатов организаций по видам экономической деятельности»</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -537,1011 +537,1121 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Прибыль, убыток (-) до налого-обложения</t>
+          <t>тысяч рублей / Прибыль (убыток) до налого-обложения</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4 (столбец D)</t>
+          <t>7 (столбец G)</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>В Word колонка называется «тысяч рублей / Прибыль (убыток) до налого-обложения», в Excel — «прибыль убыток от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t23-прVed14.xlsx, колонка 7 (столбец G).</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «прибыль убыток от продолжающейся деятельности до налогообложения» на «тысяч рублей / Прибыль (убыток) до налого-обложения».
+Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t23-прVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «тысяч рублей / Прибыль (убыток) до налого-обложения».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Таблица 14 «Формирование финансовых результатов организаций по видам экономической деятельности», страница «Продолжение таблицы 14»</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>предоставление услуг в области добычи полезных ископаемых</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Прибыль (убыток) до налого-обложения</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7 (столбец G)</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>В Word колонка называется «Прибыль (убыток) до налого-обложения», в Excel — «прибыль убыток от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t23-прVed14.xlsx, колонка 7 (столбец G).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «прибыль убыток от продолжающейся деятельности до налогообложения» на «Прибыль (убыток) до налого-обложения».
+Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t23-прVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль (убыток) до налого-обложения».</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Таблица «15. группировка организаций, получивших прибыль или убыток, по видам экономической деятельности»</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Прибыль, убыток (-) до налого-обложения</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>S25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4 (столбец D)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>72</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Таблица 15 «Группировка организаций, получивших прибыль или убыток, по видам экономической деятельности», страница «Продолжение таблицы 15»</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>производство текстильных изделий</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I6" t="n">
         <v>72</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Таблица «16. группировка организаций, получивших прибыль или убыток, по муниципальным образованиям камчатского края»</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Камчатский край</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>87</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25Ved14mo8.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25Ved14mo8.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Таблица «17. группировка организаций, получивших прибыль или убыток, по организационно-правовым формам»</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Организационно-правовые формы юридических лиц, являющихся коммерческими корпоративными организациями</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I8" t="n">
         <v>102</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25OpfVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25OpfVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Таблица 17 «Группировка организаций, получивших прибыль или убыток, по организационно-правовым формам», страница «Продолжение таблицы 17»</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>потребительские кооперативы</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I9" t="n">
         <v>102</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25OpfVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25OpfVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Таблица «18. группировка организаций, получивших прибыль или убыток, по формам собственности»</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налого-обложения</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>117</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налого-обложения», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t25FsVed14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения» на «Прибыль, убыток (-) до налого-обложения».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t25FsVed14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налого-обложения».</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Строка не узнана</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Таблица 18</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Название строки «Всего» не найдено в справочнике категорий (из самого Excel-файла). Строка не заполнена — в ней прочерки.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Похожей строки в справочнике нет. Если эта строка есть в Excel-источнике (S25_000000_t25FsVed14.xlsx) — добавьте её в справочник: строка «код;название», код как в первой колонке Excel, название как в Word. Если в Excel её нет — прочерк правильный, ничего делать не нужно.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / всем активам</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>3 (столбец C)</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" t="n">
         <v>142</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / всем активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 3 (столбец C).</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам» на «Прибыль, убыток (-) до налогообложения в % к / всем активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / всем активам».</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>143</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>5 (столбец E)</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>144</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 5 (столбец E).</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>6 (столбец F)</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>145</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 6 (столбец F).</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам» на «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>7 (столбец G)</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>146</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 7 (столбец G).</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Таблица «20. уровень рентабельности (убыточности) активов организаций по видам экономической деятельности»</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>8 (столбец H)</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I17" t="n">
         <v>147</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 8 (столбец H).</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / всем активам</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>3 (столбец C)</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>142</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>10</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / всем активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 3 (столбец C).</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: всем активам» на «Прибыль, убыток (-) до налогообложения в % к / всем активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / всем активам».</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>4 (столбец D)</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I19" t="n">
         <v>143</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 4 (столбец D).</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: внеоборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / вне-оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>5 (столбец E)</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I20" t="n">
         <v>144</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 5 (столбец E).</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: оборотным активам» на «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / оборот-ным активам».</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>6 (столбец F)</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>145</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>10</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 6 (столбец F).</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: капиталу и резервам» на «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / капиталу и резервам».</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>7 (столбец G)</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I22" t="n">
         <v>146</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 7 (столбец G).</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: долгосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / долго-срочным обяза-тельствам».</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>В Excel лишние слова «от продолжающейся деятельности»</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Таблица 20 «Уровень рентабельности (убыточности) активов организаций по видам экономической деятельности», страница «Продолжение таблицы 20»</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Обрабатывающие производства</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>S25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>8 (столбец H)</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>147</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>10</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>В Word колонка называется «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам», в Excel — «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам». Без слов «от продолжающейся деятельности» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из S25_000000_t27Ved14.xlsx, колонка 8 (столбец H).</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Прибыль (убыток) от продолжающейся деятельности до налогообложения в % к: краткосрочным обязательствам» на «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике S25_000000_t27Ved14.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Прибыль, убыток (-) до налогообложения в % к / кратко-срочным обяза-тельствам».</t>

--- a/output/проверьте_названия_Word_и_Excel.xlsx
+++ b/output/проверьте_названия_Word_и_Excel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,40 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Строка в Word</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Колонка в Word</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Excel-источник</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Показатель в Excel</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Колонка Excel</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Строка в column_mapping_v2.csv</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Сколько страниц</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Что сделала программа</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Что сделать</t>
         </is>
@@ -476,51 +481,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Строка не узнана</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Таблицы 4, 6, 7, 8, 9, 10, 11, 12, 13, 16, 19, 21, 23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Название строки «деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей» не найдено в справочнике ОКВЭД (input/mappings/okved_mapping.csv). Строка не заполнена — в ней прочерки.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Похожей строки в справочнике нет. Если эта строка есть в Excel-источнике (M25_000000_t01Ved14.xlsx) — добавьте её в справочник: строка «код;название», код как в первой колонке Excel, название как в Word. Если в Excel её нет — прочерк правильный, ничего делать не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Строка не узнана</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Таблица 17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Название строки «Всего» не найдено в справочнике категорий (из самого Excel-файла). Строка не заполнена — в ней прочерки.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Похожей строки в справочнике нет. Если эта строка есть в Excel-источнике (M25_000000_t25FsVed14.xlsx) — добавьте её в справочник: строка «код;название», код как в первой колонке Excel, название как в Word. Если в Excel её нет — прочерк правильный, ничего делать не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Названия отличаются словом в скобках</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Таблица 18 «Группировка организаций, получивших прибыль или убыток, по муниципальным образованиям камчатского края», страница «Продолжение таблицы 18»</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Камчатский край</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Темп роста прибыли, в %</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Темп роста прибыли (убытка) в %</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12 (столбец L)</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I4" t="n">
         <v>118</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>В Word колонка называется «Темп роста прибыли, в %», в Excel — «Темп роста прибыли (убытка) в %». Без слова «(убытка)» в скобках названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из M25_000000_t25Ved14mo8.xlsx, колонка 12 (столбец L).</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>В Word колонка называется «Темп роста прибыли, в %», в Excel — «Темп роста прибыли (убытка) в %». Без слова «(убытка)» названия совпадают, поэтому программа сочла их одним показателем и поставила в колонку числа из M25_000000_t25Ved14mo8.xlsx, колонка 12 (столбец L).</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Если числа верные — ничего делать не нужно. Чтобы строка больше не появлялась, в input/mappings/column_mapping_v2.csv (строка указана слева) в поле «Название показателя» замените «Темп роста прибыли (убытка) в %» на «Темп роста прибыли, в %».
 Если числа неверные (в колонке Word другой показатель) — сделайте так, чтобы нужный показатель назывался в Word и в Excel одинаково. Любой из способов: 1) в Word (input/Бюллетень.docx) переименуйте колонку так, как нужный показатель назван в Excel; 2) в Excel-источнике M25_000000_t25Ved14mo8.xlsx переименуйте нужный показатель так, как колонка названа в Word; 3) в input/mappings/column_mapping_v2.csv найдите строку нужного показателя этого файла и в поле «Название показателя» впишите «Темп роста прибыли, в %».</t>
